--- a/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD7861D9-EF7F-44C9-AF86-07026B822006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D738D96B-1E48-4E51-A63F-A9EE01639A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{73424153-0203-44DC-B433-CD8F7E07313C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CFE8CC2E-248B-4327-8EA7-ABFCDD213FE0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D067F82-A163-4D0F-8344-6F617698B409}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A468DBE-F9FA-4012-A214-0967AC9C67B8}">
   <dimension ref="B3:L214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D738D96B-1E48-4E51-A63F-A9EE01639A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4244984-12FF-49DA-8BBE-31550161D7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CFE8CC2E-248B-4327-8EA7-ABFCDD213FE0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{438C0884-0FB4-42E6-9880-EB14263FF3CB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A468DBE-F9FA-4012-A214-0967AC9C67B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D57DC86-CB82-4EF7-B8B6-9A061DE73106}">
   <dimension ref="B3:L214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4244984-12FF-49DA-8BBE-31550161D7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E29373A8-E629-47E2-842F-C62AEC419807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{438C0884-0FB4-42E6-9880-EB14263FF3CB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{188364AF-D647-4119-AEEE-2758FC9ED2CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D57DC86-CB82-4EF7-B8B6-9A061DE73106}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B548816-A183-4F81-A535-E0BB54280AEA}">
   <dimension ref="B3:L214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E29373A8-E629-47E2-842F-C62AEC419807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D2C84A2-77EA-45CE-908C-9966ECA4F211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{188364AF-D647-4119-AEEE-2758FC9ED2CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{847D8D25-57C3-4751-A940-01EA3F800DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B548816-A183-4F81-A535-E0BB54280AEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4CA5E7-2409-490A-BC4B-E6C8F4C83A7E}">
   <dimension ref="B3:L214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D2C84A2-77EA-45CE-908C-9966ECA4F211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA5D52FC-A340-40CD-BD12-BA6E16618EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{847D8D25-57C3-4751-A940-01EA3F800DDF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{92094AEA-7947-4C66-9BC4-F48258F42CD8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4CA5E7-2409-490A-BC4B-E6C8F4C83A7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB14594C-3B8C-47C4-9FF1-144CA9907072}">
   <dimension ref="B3:L214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
